--- a/ig/mc-add-link-doc/StructureDefinition-as-device.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -463,7 +463,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de l'identifiant métier de l'autorisation ARHGOS d’un équipement matériel lourd.</t>
   </si>
   <si>
-    <t>Synonyme MOS : numeroAutorisationARHGOS</t>
+    <t>Synonyme : numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t>Device.extension:as-ext-device-authorization-date-device</t>
@@ -525,6 +525,9 @@
   </si>
   <si>
     <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
+  </si>
+  <si>
+    <t>Synonyme MOS : numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t>.id</t>
@@ -3131,7 +3134,7 @@
         <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3196,21 +3199,21 @@
         <v>94</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3233,16 +3236,16 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3292,7 +3295,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3304,10 +3307,10 @@
         <v>93</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>74</v>
@@ -3318,10 +3321,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3344,16 +3347,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3403,7 +3406,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3418,10 +3421,10 @@
         <v>94</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>74</v>
@@ -3429,10 +3432,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3455,13 +3458,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3512,7 +3515,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3538,10 +3541,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3570,7 +3573,7 @@
         <v>130</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>132</v>
@@ -3623,7 +3626,7 @@
         <v>135</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3649,14 +3652,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3678,10 +3681,10 @@
         <v>129</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>132</v>
@@ -3736,7 +3739,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3762,14 +3765,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3788,16 +3791,16 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3847,7 +3850,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3862,25 +3865,25 @@
         <v>94</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3902,13 +3905,13 @@
         <v>97</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3958,7 +3961,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3973,21 +3976,21 @@
         <v>94</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4013,16 +4016,16 @@
         <v>97</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>74</v>
@@ -4071,7 +4074,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -4086,7 +4089,7 @@
         <v>94</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>74</v>
@@ -4097,14 +4100,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4123,16 +4126,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4182,7 +4185,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -4197,25 +4200,25 @@
         <v>94</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4234,16 +4237,16 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4293,7 +4296,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4308,21 +4311,21 @@
         <v>94</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4348,16 +4351,16 @@
         <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>74</v>
@@ -4382,13 +4385,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4406,7 +4409,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -4421,7 +4424,7 @@
         <v>94</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>74</v>
@@ -4432,10 +4435,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4461,13 +4464,13 @@
         <v>104</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4493,13 +4496,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4517,7 +4520,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4532,10 +4535,10 @@
         <v>94</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>74</v>
@@ -4543,10 +4546,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4569,16 +4572,16 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4604,13 +4607,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -4628,7 +4631,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4643,10 +4646,10 @@
         <v>94</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>74</v>
@@ -4654,14 +4657,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4680,16 +4683,16 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4739,7 +4742,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4754,21 +4757,21 @@
         <v>94</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4791,16 +4794,16 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4850,7 +4853,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4865,10 +4868,10 @@
         <v>94</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>95</v>
@@ -4876,10 +4879,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4902,13 +4905,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4959,7 +4962,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4974,21 +4977,21 @@
         <v>94</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5011,13 +5014,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5068,7 +5071,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -5083,21 +5086,21 @@
         <v>94</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5120,16 +5123,16 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5179,7 +5182,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -5194,21 +5197,21 @@
         <v>94</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5231,16 +5234,16 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5290,7 +5293,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5305,10 +5308,10 @@
         <v>94</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>74</v>
@@ -5316,10 +5319,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5342,13 +5345,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5399,7 +5402,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5425,10 +5428,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5451,13 +5454,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5508,7 +5511,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5534,10 +5537,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5566,7 +5569,7 @@
         <v>130</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>132</v>
@@ -5619,7 +5622,7 @@
         <v>135</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5645,14 +5648,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5674,10 +5677,10 @@
         <v>129</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>132</v>
@@ -5732,7 +5735,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -5758,14 +5761,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5784,16 +5787,16 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5843,7 +5846,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5869,10 +5872,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5898,13 +5901,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5930,13 +5933,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5954,7 +5957,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5969,10 +5972,10 @@
         <v>94</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>74</v>
@@ -5980,10 +5983,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6006,16 +6009,16 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6065,7 +6068,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -6080,10 +6083,10 @@
         <v>94</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>74</v>
@@ -6091,10 +6094,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6117,16 +6120,16 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6176,7 +6179,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -6191,10 +6194,10 @@
         <v>94</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>74</v>
@@ -6202,10 +6205,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6228,16 +6231,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6263,13 +6266,13 @@
         <v>74</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>74</v>
@@ -6287,7 +6290,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -6302,7 +6305,7 @@
         <v>94</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>74</v>
@@ -6313,10 +6316,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6339,13 +6342,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6396,7 +6399,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -6422,10 +6425,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6448,13 +6451,13 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6505,7 +6508,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6531,10 +6534,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6563,7 +6566,7 @@
         <v>130</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>132</v>
@@ -6616,7 +6619,7 @@
         <v>135</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6642,14 +6645,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6671,10 +6674,10 @@
         <v>129</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>132</v>
@@ -6729,7 +6732,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6755,14 +6758,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6781,16 +6784,16 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6840,7 +6843,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6855,7 +6858,7 @@
         <v>94</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>74</v>
@@ -6866,10 +6869,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6892,16 +6895,16 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6951,7 +6954,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6969,7 +6972,7 @@
         <v>102</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>74</v>
@@ -6977,10 +6980,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7003,13 +7006,13 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7060,7 +7063,7 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
@@ -7086,10 +7089,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7112,13 +7115,13 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7169,7 +7172,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -7195,10 +7198,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7227,7 +7230,7 @@
         <v>130</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>132</v>
@@ -7280,7 +7283,7 @@
         <v>135</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -7306,14 +7309,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7335,10 +7338,10 @@
         <v>129</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>132</v>
@@ -7393,7 +7396,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>75</v>
@@ -7419,14 +7422,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7445,16 +7448,16 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7504,7 +7507,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7519,7 +7522,7 @@
         <v>94</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>74</v>
@@ -7530,10 +7533,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7559,10 +7562,10 @@
         <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7613,7 +7616,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7628,10 +7631,10 @@
         <v>94</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>74</v>
@@ -7639,10 +7642,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7665,16 +7668,16 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7724,7 +7727,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7750,10 +7753,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7776,13 +7779,13 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7833,7 +7836,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7859,10 +7862,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7885,13 +7888,13 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7942,7 +7945,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7968,10 +7971,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8000,7 +8003,7 @@
         <v>130</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>132</v>
@@ -8053,7 +8056,7 @@
         <v>135</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
@@ -8079,14 +8082,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8108,10 +8111,10 @@
         <v>129</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>132</v>
@@ -8166,7 +8169,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -8192,10 +8195,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8218,16 +8221,16 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8277,7 +8280,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8292,7 +8295,7 @@
         <v>94</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>74</v>
@@ -8303,10 +8306,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8329,16 +8332,16 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8388,7 +8391,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
@@ -8400,10 +8403,10 @@
         <v>93</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>74</v>
@@ -8414,10 +8417,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8440,16 +8443,16 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8499,7 +8502,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>75</v>
@@ -8514,7 +8517,7 @@
         <v>94</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>74</v>
@@ -8525,10 +8528,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8551,19 +8554,19 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>74</v>
@@ -8612,7 +8615,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>75</v>
@@ -8624,13 +8627,13 @@
         <v>93</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>74</v>
@@ -8638,10 +8641,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8664,16 +8667,16 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8723,7 +8726,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
@@ -8735,13 +8738,13 @@
         <v>93</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>74</v>
@@ -8749,10 +8752,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8775,16 +8778,16 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8834,7 +8837,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
@@ -8846,13 +8849,13 @@
         <v>93</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>74</v>
@@ -8860,10 +8863,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8886,19 +8889,19 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>74</v>
@@ -8947,7 +8950,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
@@ -8959,13 +8962,13 @@
         <v>93</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>74</v>
@@ -8973,10 +8976,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9002,13 +9005,13 @@
         <v>97</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9058,7 +9061,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>75</v>
@@ -9073,10 +9076,10 @@
         <v>94</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>74</v>
@@ -9084,10 +9087,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9110,16 +9113,16 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9169,7 +9172,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
@@ -9184,7 +9187,7 @@
         <v>94</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>74</v>
@@ -9195,10 +9198,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9221,16 +9224,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9280,7 +9283,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9295,7 +9298,7 @@
         <v>94</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>74</v>
@@ -9306,10 +9309,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9332,16 +9335,16 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9391,7 +9394,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9403,10 +9406,10 @@
         <v>93</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>74</v>
